--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -646,7 +646,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -740,7 +740,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -887,7 +887,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -911,7 +911,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -1003,7 +1003,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1077,7 +1077,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1455,7 +1455,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1475,7 +1475,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
